--- a/data/experiments.xlsx
+++ b/data/experiments.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA433"/>
+  <dimension ref="A1:BA462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47888,18 +47888,23 @@
       <c r="AM274" t="n">
         <v>0.0304</v>
       </c>
+      <c r="AN274" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.8682(limit 0.7):FAIL</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>8/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="AQ274" t="n">
-        <v>0.5909</v>
+        <v>0.8682</v>
       </c>
       <c r="AS274" t="b">
         <v>1</v>
@@ -69981,7 +69986,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-09-10T13:55:59+00:00</t>
+          <t>2026-09-12T01:33:48+00:00</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -69991,7 +69996,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>TIMEOUT</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -70071,7 +70076,7 @@
       </c>
       <c r="AT398" t="inlineStr">
         <is>
-          <t>Status TIMEOUT != COMPLETED (simulation 3qwwOa7r24job22QcQRjQik did not finish within 30s (last progress=0.1) | expr='r33d_v2ckp_d12')</t>
+          <t>Status FAILED != COMPLETED (Not found. | expr='r33d_v2ckp_d12')</t>
         </is>
       </c>
       <c r="AU398" t="n">
@@ -70085,7 +70090,7 @@
       </c>
       <c r="BA398" t="inlineStr">
         <is>
-          <t>simulation 3qwwOa7r24job22QcQRjQik did not finish within 30s (last progress=0.1) | expr='r33d_v2ckp_d12'</t>
+          <t>Not found. | expr='r33d_v2ckp_d12'</t>
         </is>
       </c>
     </row>
@@ -74255,18 +74260,23 @@
       <c r="AM420" t="n">
         <v>0.0348</v>
       </c>
+      <c r="AN420" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.9738(limit 0.7):FAIL</t>
+        </is>
+      </c>
       <c r="AO420" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AP420" t="inlineStr">
         <is>
-          <t>8/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="AQ420" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.9738</v>
       </c>
       <c r="AS420" t="b">
         <v>1</v>
@@ -75237,18 +75247,23 @@
       <c r="AM425" t="n">
         <v>0.0326</v>
       </c>
+      <c r="AN425" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.9664(limit 0.7):FAIL</t>
+        </is>
+      </c>
       <c r="AO425" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AP425" t="inlineStr">
         <is>
-          <t>8/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="AQ425" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.9664</v>
       </c>
       <c r="AS425" t="b">
         <v>1</v>
@@ -75602,18 +75617,23 @@
       <c r="AM427" t="n">
         <v>0.0382</v>
       </c>
+      <c r="AN427" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.7318(limit 0.7):FAIL</t>
+        </is>
+      </c>
       <c r="AO427" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AP427" t="inlineStr">
         <is>
-          <t>8/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="AQ427" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.7318</v>
       </c>
       <c r="AS427" t="b">
         <v>1</v>
@@ -76183,18 +76203,20 @@
       <c r="AM430" t="n">
         <v>0.0351</v>
       </c>
+      <c r="AN430" t="inlineStr">
+        <is>
+          <t>ALREADY_SUBMITTED:FAIL</t>
+        </is>
+      </c>
       <c r="AO430" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AP430" t="inlineStr">
         <is>
-          <t>8/8</t>
-        </is>
-      </c>
-      <c r="AQ430" t="n">
-        <v>0.628</v>
+          <t>0/8</t>
+        </is>
       </c>
       <c r="AS430" t="b">
         <v>1</v>
@@ -76221,7 +76243,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2026-09-10T13:56:02+00:00</t>
+          <t>2026-09-12T01:33:56+00:00</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -76306,6 +76328,14 @@
           <t>FASTEXPR</t>
         </is>
       </c>
+      <c r="AS431" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT431" t="inlineStr">
+        <is>
+          <t>Status FAILED != COMPLETED (Not found. | expr='r33g_r2cp_d10')</t>
+        </is>
+      </c>
       <c r="AU431" t="n">
         <v>0</v>
       </c>
@@ -76317,7 +76347,7 @@
       </c>
       <c r="BA431" t="inlineStr">
         <is>
-          <t>manual: redundant clone of d7 winner</t>
+          <t>Not found. | expr='r33g_r2cp_d10'</t>
         </is>
       </c>
     </row>
@@ -76475,18 +76505,23 @@
       <c r="AM432" t="n">
         <v>0.0342</v>
       </c>
+      <c r="AN432" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.9421(limit 0.7):FAIL</t>
+        </is>
+      </c>
       <c r="AO432" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AP432" t="inlineStr">
         <is>
-          <t>8/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="AQ432" t="n">
-        <v>0.574</v>
+        <v>0.9421</v>
       </c>
       <c r="AS432" t="b">
         <v>1</v>
@@ -76513,23 +76548,27 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2026-09-10T14:26:07+00:00</t>
+          <t>2026-09-12T01:35:39+00:00</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>r33g_r2cp_d10</t>
+          <t>r34_r3cp_d7</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>TIMEOUT</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr"/>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 120), std=3.0), subindustry); c = group_zscore(winsorize(ts_mean(rel_ret_comp, 10), std=3.0), industry); p = group_zscore(winsorize(ts_mean(pcr_oi_180, 20), std=3.0), industry); group_zscore(winsorize(r + r + c + p, std=3.0), industry)</t>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 120), std=3.0), subindustry); c = group_zscore(winsorize(ts_mean(rel_ret_comp, 10), std=3.0), industry); p = group_zscore(winsorize(ts_mean(pcr_oi_180, 20), std=3.0), industry); group_zscore(winsorize(r + r + r + c + p, std=3.0), industry)</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -76547,11 +76586,19 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>19XzB1cCL4pyaLgI94jaX8</t>
-        </is>
-      </c>
-      <c r="J433" t="inlineStr"/>
-      <c r="K433" t="inlineStr"/>
+          <t>4bZdM45lr4yUa2NuFEtVhaF</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>E5vNwdWJ</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/E5vNwdWJ</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USA</t>
@@ -76566,7 +76613,7 @@
         <v>1</v>
       </c>
       <c r="O433" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P433" t="inlineStr">
         <is>
@@ -76601,53 +76648,5818 @@
           <t>FASTEXPR</t>
         </is>
       </c>
-      <c r="W433" t="inlineStr"/>
-      <c r="X433" t="inlineStr"/>
-      <c r="Y433" t="inlineStr"/>
-      <c r="Z433" t="inlineStr"/>
-      <c r="AA433" t="inlineStr"/>
-      <c r="AB433" t="inlineStr"/>
-      <c r="AC433" t="inlineStr"/>
-      <c r="AD433" t="inlineStr"/>
-      <c r="AE433" t="inlineStr"/>
-      <c r="AF433" t="inlineStr"/>
-      <c r="AG433" t="inlineStr"/>
-      <c r="AH433" t="inlineStr"/>
-      <c r="AI433" t="inlineStr"/>
-      <c r="AJ433" t="inlineStr"/>
-      <c r="AK433" t="inlineStr"/>
-      <c r="AL433" t="inlineStr"/>
-      <c r="AM433" t="inlineStr"/>
-      <c r="AN433" t="inlineStr"/>
-      <c r="AO433" t="inlineStr"/>
-      <c r="AP433" t="inlineStr"/>
-      <c r="AQ433" t="inlineStr"/>
-      <c r="AR433" t="inlineStr"/>
+      <c r="W433" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="X433" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Y433" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="Z433" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="AA433" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="AB433" t="n">
+        <v>0.001782</v>
+      </c>
+      <c r="AC433" t="n">
+        <v>4895025</v>
+      </c>
+      <c r="AD433" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE433" t="n">
+        <v>1335</v>
+      </c>
+      <c r="AF433" t="n">
+        <v>1333</v>
+      </c>
+      <c r="AG433" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH433" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI433" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ433" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK433" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="AL433" t="n">
+        <v>0.1091</v>
+      </c>
+      <c r="AM433" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="AN433" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.9891(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO433" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP433" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ433" t="n">
+        <v>0.9891</v>
+      </c>
+      <c r="AR433" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
       <c r="AS433" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT433" t="inlineStr">
-        <is>
-          <t>Status TIMEOUT != COMPLETED (simulation 19XzB1cCL4pyaLgI94jaX8 did not finish within 1800s (last progress=0.1) | expr='r33g_r2cp_d10')</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AU433" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV433" t="n">
         <v>0</v>
       </c>
       <c r="AW433" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX433" t="inlineStr"/>
-      <c r="AY433" t="inlineStr"/>
-      <c r="AZ433" t="inlineStr"/>
-      <c r="BA433" t="inlineStr">
-        <is>
-          <t>simulation 19XzB1cCL4pyaLgI94jaX8 did not finish within 1800s (last progress=0.1) | expr='r33g_r2cp_d10'</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AX433" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY433" t="n">
+        <v>0.6825625734441252</v>
+      </c>
+      <c r="AZ433" t="n">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:35:54+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>r34_r2cp_sub_d7</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 120), std=3.0), subindustry); c = group_zscore(winsorize(ts_mean(rel_ret_comp, 10), std=3.0), subindustry); p = group_zscore(winsorize(ts_mean(pcr_oi_180, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + c + p, std=3.0), subindustry)</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, option9</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_ret_comp, pcr_oi_180</t>
+        </is>
+      </c>
+      <c r="H434" t="n">
+        <v>5</v>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>142ATa8wt4Jg8xwpflyufZN</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>npKmgEdz</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/npKmgEdz</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N434" t="n">
+        <v>1</v>
+      </c>
+      <c r="O434" t="n">
+        <v>7</v>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q434" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V434" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W434" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X434" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Y434" t="n">
+        <v>0.1229</v>
+      </c>
+      <c r="Z434" t="n">
+        <v>0.0892</v>
+      </c>
+      <c r="AA434" t="n">
+        <v>0.0396</v>
+      </c>
+      <c r="AB434" t="n">
+        <v>0.001452</v>
+      </c>
+      <c r="AC434" t="n">
+        <v>4413993</v>
+      </c>
+      <c r="AD434" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE434" t="n">
+        <v>1313</v>
+      </c>
+      <c r="AF434" t="n">
+        <v>1330</v>
+      </c>
+      <c r="AG434" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AH434" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AI434" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AJ434" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AK434" t="n">
+        <v>0.0176</v>
+      </c>
+      <c r="AL434" t="n">
+        <v>0.1212</v>
+      </c>
+      <c r="AM434" t="n">
+        <v>0.0396</v>
+      </c>
+      <c r="AN434" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.9763(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO434" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP434" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ434" t="n">
+        <v>0.9762999999999999</v>
+      </c>
+      <c r="AR434" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS434" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU434" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV434" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW434" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX434" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY434" t="n">
+        <v>0.7013558298039592</v>
+      </c>
+      <c r="AZ434" t="n">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:37:25+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>r34_r2up_d7</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 120), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); p = group_zscore(winsorize(ts_mean(pcr_oi_180, 20), std=3.0), industry); group_zscore(winsorize(r + r + u + p, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, option9</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_num_all, pcr_oi_180</t>
+        </is>
+      </c>
+      <c r="H435" t="n">
+        <v>5</v>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>yDAs87gA5bO9r1DsR65fH0</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>KPOv9lel</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/KPOv9lel</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N435" t="n">
+        <v>1</v>
+      </c>
+      <c r="O435" t="n">
+        <v>7</v>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q435" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W435" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X435" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y435" t="n">
+        <v>0.0839</v>
+      </c>
+      <c r="Z435" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="AA435" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="AB435" t="n">
+        <v>0.002391</v>
+      </c>
+      <c r="AC435" t="n">
+        <v>4964570</v>
+      </c>
+      <c r="AD435" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE435" t="n">
+        <v>1332</v>
+      </c>
+      <c r="AF435" t="n">
+        <v>1339</v>
+      </c>
+      <c r="AG435" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH435" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI435" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AJ435" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK435" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="AL435" t="n">
+        <v>0.0819</v>
+      </c>
+      <c r="AM435" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="AN435" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.7526(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO435" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP435" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ435" t="n">
+        <v>0.7526</v>
+      </c>
+      <c r="AR435" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS435" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU435" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV435" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW435" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX435" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY435" t="n">
+        <v>0.6982060345389938</v>
+      </c>
+      <c r="AZ435" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:37:44+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>r34_r2cp_k250_d7</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 250), std=3.0), subindustry); c = group_zscore(winsorize(ts_mean(rel_ret_comp, 10), std=3.0), industry); p = group_zscore(winsorize(ts_mean(pcr_oi_180, 20), std=3.0), industry); group_zscore(winsorize(r + r + c + p, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, option9</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_ret_comp, pcr_oi_180</t>
+        </is>
+      </c>
+      <c r="H436" t="n">
+        <v>5</v>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>1f8SQVbRD5dx9ZTBRJJBgo3</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>gJQXMk0Q</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/gJQXMk0Q</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N436" t="n">
+        <v>1</v>
+      </c>
+      <c r="O436" t="n">
+        <v>7</v>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q436" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W436" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="X436" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Y436" t="n">
+        <v>0.1098</v>
+      </c>
+      <c r="Z436" t="n">
+        <v>0.1031</v>
+      </c>
+      <c r="AA436" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="AB436" t="n">
+        <v>0.001879</v>
+      </c>
+      <c r="AC436" t="n">
+        <v>5103439</v>
+      </c>
+      <c r="AD436" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE436" t="n">
+        <v>1330</v>
+      </c>
+      <c r="AF436" t="n">
+        <v>1340</v>
+      </c>
+      <c r="AG436" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AH436" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AI436" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ436" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AK436" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="AL436" t="n">
+        <v>0.1072</v>
+      </c>
+      <c r="AM436" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="AN436" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.9439(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO436" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP436" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ436" t="n">
+        <v>0.9439</v>
+      </c>
+      <c r="AR436" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS436" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU436" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW436" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX436" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY436" t="n">
+        <v>1.032940785653595</v>
+      </c>
+      <c r="AZ436" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:38:00+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>r34_r2cp_k60_d7</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 60), std=3.0), subindustry); c = group_zscore(winsorize(ts_mean(rel_ret_comp, 10), std=3.0), industry); p = group_zscore(winsorize(ts_mean(pcr_oi_180, 20), std=3.0), industry); group_zscore(winsorize(r + r + c + p, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, option9</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_ret_comp, pcr_oi_180</t>
+        </is>
+      </c>
+      <c r="H437" t="n">
+        <v>5</v>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>2MF6d29nK4li9yrU1z823XQ</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>YP5806QJ</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/YP5806QJ</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N437" t="n">
+        <v>1</v>
+      </c>
+      <c r="O437" t="n">
+        <v>7</v>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q437" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W437" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X437" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y437" t="n">
+        <v>0.1451</v>
+      </c>
+      <c r="Z437" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="AA437" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="AB437" t="n">
+        <v>0.001318</v>
+      </c>
+      <c r="AC437" t="n">
+        <v>4729934</v>
+      </c>
+      <c r="AD437" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE437" t="n">
+        <v>1305</v>
+      </c>
+      <c r="AF437" t="n">
+        <v>1360</v>
+      </c>
+      <c r="AG437" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH437" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI437" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AJ437" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AK437" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="AL437" t="n">
+        <v>0.1439</v>
+      </c>
+      <c r="AM437" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="AN437" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.9359(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO437" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP437" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ437" t="n">
+        <v>0.9359</v>
+      </c>
+      <c r="AR437" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS437" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU437" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW437" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX437" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY437" t="n">
+        <v>0.6701741067314771</v>
+      </c>
+      <c r="AZ437" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:39:31+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>r34_r2cp_c20_d7</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 120), std=3.0), subindustry); c = group_zscore(winsorize(ts_mean(rel_ret_comp, 20), std=3.0), industry); p = group_zscore(winsorize(ts_mean(pcr_oi_180, 20), std=3.0), industry); group_zscore(winsorize(r + r + c + p, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, option9</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_ret_comp, pcr_oi_180</t>
+        </is>
+      </c>
+      <c r="H438" t="n">
+        <v>5</v>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>2FsGGAcMs4Za9F4MTuzH3Fm</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>O0rRZaYR</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/O0rRZaYR</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N438" t="n">
+        <v>1</v>
+      </c>
+      <c r="O438" t="n">
+        <v>7</v>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q438" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W438" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X438" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y438" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="Z438" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="AA438" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="AB438" t="n">
+        <v>0.001838</v>
+      </c>
+      <c r="AC438" t="n">
+        <v>4894364</v>
+      </c>
+      <c r="AD438" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE438" t="n">
+        <v>1319</v>
+      </c>
+      <c r="AF438" t="n">
+        <v>1350</v>
+      </c>
+      <c r="AG438" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AH438" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AI438" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AJ438" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AK438" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="AL438" t="n">
+        <v>0.1056</v>
+      </c>
+      <c r="AM438" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="AN438" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.9666(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO438" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP438" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ438" t="n">
+        <v>0.9666</v>
+      </c>
+      <c r="AR438" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS438" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU438" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW438" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX438" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY438" t="n">
+        <v>0.739476165944515</v>
+      </c>
+      <c r="AZ438" t="n">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:39:26+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>r34_r2cp_c5_d7</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 120), std=3.0), subindustry); c = group_zscore(winsorize(ts_mean(rel_ret_comp, 5), std=3.0), industry); p = group_zscore(winsorize(ts_mean(pcr_oi_180, 20), std=3.0), industry); group_zscore(winsorize(r + r + c + p, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, option9</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_ret_comp, pcr_oi_180</t>
+        </is>
+      </c>
+      <c r="H439" t="n">
+        <v>5</v>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>2kKvAqdRb4Kj9d9VBY3nhUi</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>vRkZlgRw</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/vRkZlgRw</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N439" t="n">
+        <v>1</v>
+      </c>
+      <c r="O439" t="n">
+        <v>7</v>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q439" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W439" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="X439" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Y439" t="n">
+        <v>0.1423</v>
+      </c>
+      <c r="Z439" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="AA439" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="AB439" t="n">
+        <v>0.001375</v>
+      </c>
+      <c r="AC439" t="n">
+        <v>4841957</v>
+      </c>
+      <c r="AD439" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE439" t="n">
+        <v>1322</v>
+      </c>
+      <c r="AF439" t="n">
+        <v>1347</v>
+      </c>
+      <c r="AG439" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH439" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AI439" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AJ439" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AK439" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="AL439" t="n">
+        <v>0.1402</v>
+      </c>
+      <c r="AM439" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="AN439" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.9774(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO439" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP439" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ439" t="n">
+        <v>0.9774</v>
+      </c>
+      <c r="AR439" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS439" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU439" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW439" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX439" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY439" t="n">
+        <v>0.8162669089621768</v>
+      </c>
+      <c r="AZ439" t="n">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:40:02+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>r34_r2cp_p10_d7</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 120), std=3.0), subindustry); c = group_zscore(winsorize(ts_mean(rel_ret_comp, 10), std=3.0), industry); p = group_zscore(winsorize(ts_mean(pcr_oi_180, 10), std=3.0), industry); group_zscore(winsorize(r + r + c + p, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, option9</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_ret_comp, pcr_oi_180</t>
+        </is>
+      </c>
+      <c r="H440" t="n">
+        <v>5</v>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>3mBGYP5ey4UvbkPCmgitqkM</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>d5OY0wgJ</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/d5OY0wgJ</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N440" t="n">
+        <v>1</v>
+      </c>
+      <c r="O440" t="n">
+        <v>7</v>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q440" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W440" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X440" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y440" t="n">
+        <v>0.1244</v>
+      </c>
+      <c r="Z440" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="AA440" t="n">
+        <v>0.0341</v>
+      </c>
+      <c r="AB440" t="n">
+        <v>0.001531</v>
+      </c>
+      <c r="AC440" t="n">
+        <v>4710876</v>
+      </c>
+      <c r="AD440" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE440" t="n">
+        <v>1320</v>
+      </c>
+      <c r="AF440" t="n">
+        <v>1348</v>
+      </c>
+      <c r="AG440" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH440" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AI440" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AJ440" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AK440" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="AL440" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="AM440" t="n">
+        <v>0.0341</v>
+      </c>
+      <c r="AN440" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.9969(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO440" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP440" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ440" t="n">
+        <v>0.9969</v>
+      </c>
+      <c r="AR440" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS440" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU440" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW440" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX440" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY440" t="n">
+        <v>0.8314395147373419</v>
+      </c>
+      <c r="AZ440" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:41:32+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>r34_r2cp2_d7</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 120), std=3.0), subindustry); c = group_zscore(winsorize(ts_mean(rel_ret_comp, 10), std=3.0), industry); p = group_zscore(winsorize(ts_mean(pcr_oi_180, 20), std=3.0), industry); group_zscore(winsorize(r + r + c + p + p, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, option9</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_ret_comp, pcr_oi_180</t>
+        </is>
+      </c>
+      <c r="H441" t="n">
+        <v>5</v>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>4FRvgXen755kcvFi1B2Zwyf</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>LL9E1qja</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/LL9E1qja</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N441" t="n">
+        <v>1</v>
+      </c>
+      <c r="O441" t="n">
+        <v>7</v>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q441" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W441" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X441" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y441" t="n">
+        <v>0.1138</v>
+      </c>
+      <c r="Z441" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AA441" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="AB441" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AC441" t="n">
+        <v>4502865</v>
+      </c>
+      <c r="AD441" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE441" t="n">
+        <v>1269</v>
+      </c>
+      <c r="AF441" t="n">
+        <v>1399</v>
+      </c>
+      <c r="AG441" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH441" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI441" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AJ441" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK441" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="AL441" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="AM441" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="AN441" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.9745(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO441" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP441" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ441" t="n">
+        <v>0.9745</v>
+      </c>
+      <c r="AR441" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS441" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU441" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW441" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX441" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY441" t="n">
+        <v>0.6604733151308991</v>
+      </c>
+      <c r="AZ441" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:41:23+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>r34_r2cop_d7</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 120), std=3.0), subindustry); c = group_zscore(winsorize(ts_mean(rel_ret_comp, 10), std=3.0), industry); o = group_zscore(winsorize(ts_mean(operating_income / cap, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + c + o, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, fundamental6</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_ret_comp, operating_income</t>
+        </is>
+      </c>
+      <c r="H442" t="n">
+        <v>5</v>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>9jHvbbrJ4jI8EUdPH4w7kE</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>2rO9Lq9Y</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/2rO9Lq9Y</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N442" t="n">
+        <v>1</v>
+      </c>
+      <c r="O442" t="n">
+        <v>7</v>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q442" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W442" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X442" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y442" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="Z442" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="AA442" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="AB442" t="n">
+        <v>0.001829</v>
+      </c>
+      <c r="AC442" t="n">
+        <v>5384337</v>
+      </c>
+      <c r="AD442" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE442" t="n">
+        <v>1378</v>
+      </c>
+      <c r="AF442" t="n">
+        <v>1361</v>
+      </c>
+      <c r="AG442" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH442" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI442" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AJ442" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AK442" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="AL442" t="n">
+        <v>0.1184</v>
+      </c>
+      <c r="AM442" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="AN442" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.8144(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO442" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP442" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ442" t="n">
+        <v>0.8144</v>
+      </c>
+      <c r="AR442" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS442" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU442" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW442" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX442" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY442" t="n">
+        <v>1.776626015795108</v>
+      </c>
+      <c r="AZ442" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:41:59+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>r34_r2cpo_d7</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 120), std=3.0), subindustry); c = group_zscore(winsorize(ts_mean(rel_ret_comp, 10), std=3.0), industry); p = group_zscore(winsorize(ts_mean(pcr_oi_180, 20), std=3.0), industry); o = group_zscore(winsorize(ts_mean(operating_income / cap, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + c + p + o, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, option9, fundamental6</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_ret_comp, pcr_oi_180, operating_income</t>
+        </is>
+      </c>
+      <c r="H443" t="n">
+        <v>6</v>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>2OqLtS75q4UWast10WARaOcA</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>QP3OVjnM</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/QP3OVjnM</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N443" t="n">
+        <v>1</v>
+      </c>
+      <c r="O443" t="n">
+        <v>7</v>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q443" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W443" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X443" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y443" t="n">
+        <v>0.1133</v>
+      </c>
+      <c r="Z443" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="AA443" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="AB443" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="AC443" t="n">
+        <v>5326821</v>
+      </c>
+      <c r="AD443" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE443" t="n">
+        <v>1304</v>
+      </c>
+      <c r="AF443" t="n">
+        <v>1325</v>
+      </c>
+      <c r="AG443" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH443" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AI443" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ443" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AK443" t="n">
+        <v>0.0379</v>
+      </c>
+      <c r="AL443" t="n">
+        <v>0.1126</v>
+      </c>
+      <c r="AM443" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="AN443" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.8224(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO443" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP443" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ443" t="n">
+        <v>0.8224</v>
+      </c>
+      <c r="AR443" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS443" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU443" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW443" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX443" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY443" t="n">
+        <v>1.41350627872677</v>
+      </c>
+      <c r="AZ443" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:43:06+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>r34_r2cpm_d7</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 120), std=3.0), subindustry); c = group_zscore(winsorize(ts_mean(rel_ret_comp, 10), std=3.0), industry); p = group_zscore(winsorize(ts_mean(pcr_oi_180, 20), std=3.0), industry); m = group_zscore(winsorize(-ts_mean(analyst_revision_rank_derivative, 20), std=3.0), industry); group_zscore(winsorize(r + r + c + p + m, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, option9, model16</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_ret_comp, pcr_oi_180, analyst_revision_rank_derivative</t>
+        </is>
+      </c>
+      <c r="H444" t="n">
+        <v>6</v>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>ARrtObsS4OSc8tZhFaG4Ob</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>KPOv9X0k</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/KPOv9X0k</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N444" t="n">
+        <v>1</v>
+      </c>
+      <c r="O444" t="n">
+        <v>7</v>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q444" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W444" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X444" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Y444" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="Z444" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="AA444" t="n">
+        <v>0.0379</v>
+      </c>
+      <c r="AB444" t="n">
+        <v>0.001727</v>
+      </c>
+      <c r="AC444" t="n">
+        <v>4893614</v>
+      </c>
+      <c r="AD444" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE444" t="n">
+        <v>1299</v>
+      </c>
+      <c r="AF444" t="n">
+        <v>1364</v>
+      </c>
+      <c r="AG444" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH444" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI444" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AJ444" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AK444" t="n">
+        <v>0.0336</v>
+      </c>
+      <c r="AL444" t="n">
+        <v>0.1127</v>
+      </c>
+      <c r="AM444" t="n">
+        <v>0.0379</v>
+      </c>
+      <c r="AN444" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.9428(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO444" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP444" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ444" t="n">
+        <v>0.9428</v>
+      </c>
+      <c r="AR444" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS444" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU444" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW444" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX444" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY444" t="n">
+        <v>1.0859864946981</v>
+      </c>
+      <c r="AZ444" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:01:40+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>r35_r2uo_d7</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 120), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); o = group_zscore(winsorize(ts_mean(operating_income / cap, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + u + o, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, fundamental6</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_num_all, operating_income</t>
+        </is>
+      </c>
+      <c r="H445" t="n">
+        <v>5</v>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>3lLM8I1Nw4qGbPCmrYBjuM0</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>npKm8WJE</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/npKm8WJE</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N445" t="n">
+        <v>1</v>
+      </c>
+      <c r="O445" t="n">
+        <v>7</v>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q445" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W445" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X445" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Y445" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Z445" t="n">
+        <v>0.1091</v>
+      </c>
+      <c r="AA445" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB445" t="n">
+        <v>0.002729</v>
+      </c>
+      <c r="AC445" t="n">
+        <v>5397295</v>
+      </c>
+      <c r="AD445" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE445" t="n">
+        <v>1382</v>
+      </c>
+      <c r="AF445" t="n">
+        <v>1360</v>
+      </c>
+      <c r="AG445" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH445" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI445" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AJ445" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AK445" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="AL445" t="n">
+        <v>0.0789</v>
+      </c>
+      <c r="AM445" t="n">
+        <v>0.0474</v>
+      </c>
+      <c r="AO445" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP445" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="AQ445" t="n">
+        <v>0.6505</v>
+      </c>
+      <c r="AS445" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU445" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV445" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW445" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX445" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY445" t="n">
+        <v>1.356991156935077</v>
+      </c>
+      <c r="AZ445" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:01:18+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>r35_r3uo_d7</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 120), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); o = group_zscore(winsorize(ts_mean(operating_income / cap, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + r + u + o, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, fundamental6</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_num_all, operating_income</t>
+        </is>
+      </c>
+      <c r="H446" t="n">
+        <v>5</v>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>1ULaD1d6C4YDcET19JphSSrB</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>Vk6Z3O2M</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/Vk6Z3O2M</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N446" t="n">
+        <v>1</v>
+      </c>
+      <c r="O446" t="n">
+        <v>7</v>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q446" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V446" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W446" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X446" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Y446" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="Z446" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="AA446" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="AB446" t="n">
+        <v>0.00251</v>
+      </c>
+      <c r="AC446" t="n">
+        <v>5367921</v>
+      </c>
+      <c r="AD446" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE446" t="n">
+        <v>1392</v>
+      </c>
+      <c r="AF446" t="n">
+        <v>1350</v>
+      </c>
+      <c r="AG446" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH446" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AI446" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AJ446" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK446" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="AL446" t="n">
+        <v>0.0851</v>
+      </c>
+      <c r="AM446" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="AN446" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.7265(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO446" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP446" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ446" t="n">
+        <v>0.7265</v>
+      </c>
+      <c r="AR446" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS446" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU446" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW446" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX446" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY446" t="n">
+        <v>1.161507640956356</v>
+      </c>
+      <c r="AZ446" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:01:56+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>r35_r3co_d7</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 120), std=3.0), subindustry); c = group_zscore(winsorize(ts_mean(rel_ret_comp, 10), std=3.0), industry); o = group_zscore(winsorize(ts_mean(operating_income / cap, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + r + c + o, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, fundamental6</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_ret_comp, operating_income</t>
+        </is>
+      </c>
+      <c r="H447" t="n">
+        <v>5</v>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>2HSl8gdcg4FO9XiOFtzzHWV</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>vRkZvmAv</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/vRkZvmAv</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N447" t="n">
+        <v>1</v>
+      </c>
+      <c r="O447" t="n">
+        <v>7</v>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q447" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W447" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="X447" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Y447" t="n">
+        <v>0.1093</v>
+      </c>
+      <c r="Z447" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="AA447" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="AB447" t="n">
+        <v>0.001963</v>
+      </c>
+      <c r="AC447" t="n">
+        <v>5307999</v>
+      </c>
+      <c r="AD447" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE447" t="n">
+        <v>1379</v>
+      </c>
+      <c r="AF447" t="n">
+        <v>1360</v>
+      </c>
+      <c r="AG447" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH447" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AI447" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AJ447" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AK447" t="n">
+        <v>0.0334</v>
+      </c>
+      <c r="AL447" t="n">
+        <v>0.1083</v>
+      </c>
+      <c r="AM447" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="AN447" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.8784(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO447" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP447" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ447" t="n">
+        <v>0.8784</v>
+      </c>
+      <c r="AR447" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS447" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU447" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW447" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX447" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY447" t="n">
+        <v>1.542994923301219</v>
+      </c>
+      <c r="AZ447" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:03:08+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>r35_s2uo_d7</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; os = operating_income / cap; s2 = ey + np + os; r = group_zscore(winsorize(ts_rank(s2, 120), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); o = group_zscore(winsorize(ts_mean(os, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + u + o, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, fundamental6, pv13</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, operating_income, rel_num_all</t>
+        </is>
+      </c>
+      <c r="H448" t="n">
+        <v>5</v>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>2GBkukd0R4rrcMp1aGKATDn9</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>blRJdd0p</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/blRJdd0p</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N448" t="n">
+        <v>1</v>
+      </c>
+      <c r="O448" t="n">
+        <v>7</v>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q448" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W448" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X448" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Y448" t="n">
+        <v>0.0796</v>
+      </c>
+      <c r="Z448" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="AA448" t="n">
+        <v>0.08309999999999999</v>
+      </c>
+      <c r="AB448" t="n">
+        <v>0.002695</v>
+      </c>
+      <c r="AC448" t="n">
+        <v>5307192</v>
+      </c>
+      <c r="AD448" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE448" t="n">
+        <v>1374</v>
+      </c>
+      <c r="AF448" t="n">
+        <v>1347</v>
+      </c>
+      <c r="AG448" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH448" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI448" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AJ448" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK448" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="AL448" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="AM448" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="AO448" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP448" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="AQ448" t="n">
+        <v>0.6227</v>
+      </c>
+      <c r="AS448" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU448" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV448" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW448" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX448" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY448" t="n">
+        <v>1.348193235408041</v>
+      </c>
+      <c r="AZ448" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:03:21+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>r35_c3rp_d7</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 120), std=3.0), subindustry); c = group_zscore(winsorize(ts_mean(rel_ret_comp, 10), std=3.0), industry); p = group_zscore(winsorize(ts_mean(pcr_oi_180, 20), std=3.0), industry); group_zscore(winsorize(c + c + c + r + p, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, option9</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_ret_comp, pcr_oi_180</t>
+        </is>
+      </c>
+      <c r="H449" t="n">
+        <v>5</v>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>llGLw3ib5gucnW10DzGM29j</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>QP3O9GKQ</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/QP3O9GKQ</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N449" t="n">
+        <v>1</v>
+      </c>
+      <c r="O449" t="n">
+        <v>7</v>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q449" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V449" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W449" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X449" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Y449" t="n">
+        <v>0.1974</v>
+      </c>
+      <c r="Z449" t="n">
+        <v>0.0618</v>
+      </c>
+      <c r="AA449" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="AB449" t="n">
+        <v>0.000626</v>
+      </c>
+      <c r="AC449" t="n">
+        <v>3059345</v>
+      </c>
+      <c r="AD449" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE449" t="n">
+        <v>1316</v>
+      </c>
+      <c r="AF449" t="n">
+        <v>1353</v>
+      </c>
+      <c r="AG449" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH449" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AI449" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AJ449" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK449" t="n">
+        <v>0.0282</v>
+      </c>
+      <c r="AL449" t="n">
+        <v>0.1969</v>
+      </c>
+      <c r="AM449" t="n">
+        <v>0.0288</v>
+      </c>
+      <c r="AN449" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=0.87(limit 1.0):FAIL</t>
+        </is>
+      </c>
+      <c r="AO449" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP449" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
+      <c r="AR449" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS449" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT449" t="inlineStr">
+        <is>
+          <t>Fitness 0.87 &lt; 1.00</t>
+        </is>
+      </c>
+      <c r="AU449" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV449" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW449" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX449" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY449" t="n">
+        <v>1.583274560312687</v>
+      </c>
+      <c r="AZ449" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:03:35+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>r35_prodrcp_d7</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 120), std=3.0), subindustry); c = group_zscore(winsorize(ts_mean(rel_ret_comp, 10), std=3.0), industry); p = group_zscore(winsorize(ts_mean(pcr_oi_180, 20), std=3.0), industry); group_zscore(winsorize(r * c * p, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, option9</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_ret_comp, pcr_oi_180</t>
+        </is>
+      </c>
+      <c r="H450" t="n">
+        <v>5</v>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>dtvFW9GE4Ca9bvnI6NLFVg</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>d5OYRjqg</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/d5OYRjqg</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N450" t="n">
+        <v>1</v>
+      </c>
+      <c r="O450" t="n">
+        <v>7</v>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q450" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T450" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V450" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W450" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="X450" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="Y450" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="Z450" t="n">
+        <v>-0.0124</v>
+      </c>
+      <c r="AA450" t="n">
+        <v>0.1436</v>
+      </c>
+      <c r="AB450" t="n">
+        <v>-9.6e-05</v>
+      </c>
+      <c r="AC450" t="n">
+        <v>-615617</v>
+      </c>
+      <c r="AD450" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE450" t="n">
+        <v>1326</v>
+      </c>
+      <c r="AF450" t="n">
+        <v>1343</v>
+      </c>
+      <c r="AG450" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="AH450" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AI450" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AJ450" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AK450" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="AL450" t="n">
+        <v>0.2586</v>
+      </c>
+      <c r="AM450" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="AN450" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=-0.08(limit 1.0):FAIL, LOW_SHARPE=-0.38(limit 1.25):FAIL</t>
+        </is>
+      </c>
+      <c r="AO450" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP450" t="inlineStr">
+        <is>
+          <t>5/8</t>
+        </is>
+      </c>
+      <c r="AR450" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS450" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT450" t="inlineStr">
+        <is>
+          <t>Sharpe -0.38 &lt; 1.25; Fitness -0.08 &lt; 1.00; Positive years 2/4 = 50.0% &lt; 60.0%; Negative-sharpe years 2 &gt; 1</t>
+        </is>
+      </c>
+      <c r="AU450" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV450" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW450" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX450" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY450" t="n">
+        <v>1.59614118005478</v>
+      </c>
+      <c r="AZ450" t="n">
+        <v>-3.02</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>p35_snt_v_p</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>group_zscore(winsorize(ts_mean(snt_social_value, 5), std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>socialmedia8</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>snt_social_value</t>
+        </is>
+      </c>
+      <c r="H451" t="n">
+        <v>1</v>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>69AUN2Ah51QbiXR25tnh5g</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>blRJd8Xq</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/blRJd8Xq</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N451" t="n">
+        <v>1</v>
+      </c>
+      <c r="O451" t="n">
+        <v>12</v>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q451" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W451" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="X451" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Y451" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="Z451" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="AA451" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="AB451" t="n">
+        <v>0.000176</v>
+      </c>
+      <c r="AC451" t="n">
+        <v>804270</v>
+      </c>
+      <c r="AD451" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE451" t="n">
+        <v>1466</v>
+      </c>
+      <c r="AF451" t="n">
+        <v>1665</v>
+      </c>
+      <c r="AG451" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AH451" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AI451" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="AJ451" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AK451" t="n">
+        <v>-0.0639</v>
+      </c>
+      <c r="AL451" t="n">
+        <v>0.1762</v>
+      </c>
+      <c r="AM451" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="AN451" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=0.11(limit 1.0):FAIL, LOW_SHARPE=0.37(limit 1.25):FAIL</t>
+        </is>
+      </c>
+      <c r="AO451" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP451" t="inlineStr">
+        <is>
+          <t>5/8</t>
+        </is>
+      </c>
+      <c r="AR451" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS451" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT451" t="inlineStr">
+        <is>
+          <t>Sharpe 0.37 &lt; 1.25; Fitness 0.11 &lt; 1.00</t>
+        </is>
+      </c>
+      <c r="AU451" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV451" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW451" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX451" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY451" t="n">
+        <v>0.548718203330878</v>
+      </c>
+      <c r="AZ451" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:05:17+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>p35_snt_v_n</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>group_zscore(winsorize(-ts_mean(snt_social_value, 5), std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>socialmedia8</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>snt_social_value</t>
+        </is>
+      </c>
+      <c r="H452" t="n">
+        <v>1</v>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>1v1xM6gUX4hD8CceHriGyPX</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>QP3O9Yag</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/QP3O9Yag</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N452" t="n">
+        <v>1</v>
+      </c>
+      <c r="O452" t="n">
+        <v>12</v>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q452" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T452" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V452" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W452" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="X452" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="Y452" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="Z452" t="n">
+        <v>-0.0163</v>
+      </c>
+      <c r="AA452" t="n">
+        <v>0.1608</v>
+      </c>
+      <c r="AB452" t="n">
+        <v>-0.000176</v>
+      </c>
+      <c r="AC452" t="n">
+        <v>-804272</v>
+      </c>
+      <c r="AD452" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE452" t="n">
+        <v>1665</v>
+      </c>
+      <c r="AF452" t="n">
+        <v>1466</v>
+      </c>
+      <c r="AG452" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AH452" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AI452" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ452" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK452" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="AL452" t="n">
+        <v>0.1762</v>
+      </c>
+      <c r="AM452" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="AN452" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=-0.11(limit 1.0):FAIL, LOW_SHARPE=-0.37(limit 1.25):FAIL, LOW_SUB_UNIVERSE_SHARPE=-0.52(limit -0.16):FAIL</t>
+        </is>
+      </c>
+      <c r="AO452" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP452" t="inlineStr">
+        <is>
+          <t>4/8</t>
+        </is>
+      </c>
+      <c r="AR452" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS452" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT452" t="inlineStr">
+        <is>
+          <t>Sharpe -0.37 &lt; 1.25; Fitness -0.11 &lt; 1.00; Positive years 0/4 = 0.0% &lt; 60.0%; Negative-sharpe years 4 &gt; 1</t>
+        </is>
+      </c>
+      <c r="AU452" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV452" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW452" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX452" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY452" t="n">
+        <v>0.548718203330878</v>
+      </c>
+      <c r="AZ452" t="n">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:17:49+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>r36_r3uo_k250_d7</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 250), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); o = group_zscore(winsorize(ts_mean(operating_income / cap, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + r + u + o, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, fundamental6</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_num_all, operating_income</t>
+        </is>
+      </c>
+      <c r="H453" t="n">
+        <v>5</v>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>3RPN0u4Eq5eOb05NF7oIz3o</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>KPOvGX7N</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/KPOvGX7N</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N453" t="n">
+        <v>1</v>
+      </c>
+      <c r="O453" t="n">
+        <v>7</v>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q453" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V453" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W453" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X453" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Y453" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="Z453" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="AA453" t="n">
+        <v>0.0609</v>
+      </c>
+      <c r="AB453" t="n">
+        <v>0.003405</v>
+      </c>
+      <c r="AC453" t="n">
+        <v>5669911</v>
+      </c>
+      <c r="AD453" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE453" t="n">
+        <v>1403</v>
+      </c>
+      <c r="AF453" t="n">
+        <v>1340</v>
+      </c>
+      <c r="AG453" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH453" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AI453" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AJ453" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AK453" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="AL453" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="AM453" t="n">
+        <v>0.0466</v>
+      </c>
+      <c r="AO453" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP453" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="AQ453" t="n">
+        <v>0.6851</v>
+      </c>
+      <c r="AS453" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU453" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV453" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW453" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX453" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY453" t="n">
+        <v>1.456419696836504</v>
+      </c>
+      <c r="AZ453" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:17:47+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>r36_r4uo_k250_d7</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 250), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); o = group_zscore(winsorize(ts_mean(operating_income / cap, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + r + r + u + o, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, fundamental6</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_num_all, operating_income</t>
+        </is>
+      </c>
+      <c r="H454" t="n">
+        <v>5</v>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>x42azXE4ygczTbymsTmJg</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>qMWONPvA</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/qMWONPvA</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N454" t="n">
+        <v>1</v>
+      </c>
+      <c r="O454" t="n">
+        <v>7</v>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q454" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V454" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W454" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="X454" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Y454" t="n">
+        <v>0.0693</v>
+      </c>
+      <c r="Z454" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="AA454" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="AB454" t="n">
+        <v>0.003262</v>
+      </c>
+      <c r="AC454" t="n">
+        <v>5591892</v>
+      </c>
+      <c r="AD454" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE454" t="n">
+        <v>1403</v>
+      </c>
+      <c r="AF454" t="n">
+        <v>1340</v>
+      </c>
+      <c r="AG454" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AH454" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AI454" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AJ454" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AK454" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="AL454" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AM454" t="n">
+        <v>0.0422</v>
+      </c>
+      <c r="AN454" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.7413(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO454" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP454" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ454" t="n">
+        <v>0.7413</v>
+      </c>
+      <c r="AR454" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS454" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU454" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV454" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW454" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX454" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY454" t="n">
+        <v>1.436532282964779</v>
+      </c>
+      <c r="AZ454" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:17:58+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>r36_r3uo_k250_d5</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 250), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); o = group_zscore(winsorize(ts_mean(operating_income / cap, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + r + u + o, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, fundamental6</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_num_all, operating_income</t>
+        </is>
+      </c>
+      <c r="H455" t="n">
+        <v>5</v>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>xJxM1ak14huaqb3j7vhCwO</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>WjP3AaPO</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/WjP3AaPO</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N455" t="n">
+        <v>1</v>
+      </c>
+      <c r="O455" t="n">
+        <v>5</v>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q455" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T455" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V455" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W455" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="X455" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y455" t="n">
+        <v>0.07729999999999999</v>
+      </c>
+      <c r="Z455" t="n">
+        <v>0.1163</v>
+      </c>
+      <c r="AA455" t="n">
+        <v>0.0615</v>
+      </c>
+      <c r="AB455" t="n">
+        <v>0.00301</v>
+      </c>
+      <c r="AC455" t="n">
+        <v>5755067</v>
+      </c>
+      <c r="AD455" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE455" t="n">
+        <v>1403</v>
+      </c>
+      <c r="AF455" t="n">
+        <v>1340</v>
+      </c>
+      <c r="AG455" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH455" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI455" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AJ455" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK455" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="AL455" t="n">
+        <v>0.07480000000000001</v>
+      </c>
+      <c r="AM455" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="AO455" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP455" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="AQ455" t="n">
+        <v>0.6872</v>
+      </c>
+      <c r="AS455" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU455" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV455" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW455" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX455" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY455" t="n">
+        <v>1.455804474050917</v>
+      </c>
+      <c r="AZ455" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:19:53+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>r36_r3uo2_k250_d7</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 250), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); o = group_zscore(winsorize(ts_mean(operating_income / cap, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + r + u + o + o, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, fundamental6</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_num_all, operating_income</t>
+        </is>
+      </c>
+      <c r="H456" t="n">
+        <v>5</v>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>2FHuQz4be4X3aOIFxCboMyX</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>blRJQdkp</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/blRJQdkp</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N456" t="n">
+        <v>1</v>
+      </c>
+      <c r="O456" t="n">
+        <v>7</v>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q456" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T456" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V456" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W456" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X456" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Y456" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="Z456" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="AA456" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="AB456" t="n">
+        <v>0.003649</v>
+      </c>
+      <c r="AC456" t="n">
+        <v>5659033</v>
+      </c>
+      <c r="AD456" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE456" t="n">
+        <v>1396</v>
+      </c>
+      <c r="AF456" t="n">
+        <v>1348</v>
+      </c>
+      <c r="AG456" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH456" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI456" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AJ456" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK456" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="AL456" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AM456" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="AO456" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP456" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="AQ456" t="n">
+        <v>0.6582</v>
+      </c>
+      <c r="AS456" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU456" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV456" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW456" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX456" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY456" t="n">
+        <v>1.652291338313757</v>
+      </c>
+      <c r="AZ456" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>p36_f2_acc</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>group_zscore(winsorize(-ts_mean(ts_delta(ts_backfill(accrued_liabilities_total, 60), 66) / cap, 20), std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>fundamental2, pv1</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>accrued_liabilities_total, cap</t>
+        </is>
+      </c>
+      <c r="H457" t="n">
+        <v>2</v>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>3t5RBdcT4CRc6XzThJpyad</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>blRJQjZK</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/blRJQjZK</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N457" t="n">
+        <v>1</v>
+      </c>
+      <c r="O457" t="n">
+        <v>12</v>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q457" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T457" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V457" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W457" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="X457" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="Y457" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="Z457" t="n">
+        <v>-0.0255</v>
+      </c>
+      <c r="AA457" t="n">
+        <v>0.2058</v>
+      </c>
+      <c r="AB457" t="n">
+        <v>-0.001326</v>
+      </c>
+      <c r="AC457" t="n">
+        <v>-1262562</v>
+      </c>
+      <c r="AD457" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE457" t="n">
+        <v>736</v>
+      </c>
+      <c r="AF457" t="n">
+        <v>577</v>
+      </c>
+      <c r="AG457" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="AH457" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AI457" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="AJ457" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AK457" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="AL457" t="n">
+        <v>0.0376</v>
+      </c>
+      <c r="AM457" t="n">
+        <v>0.0541</v>
+      </c>
+      <c r="AN457" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=-0.2(limit 1.0):FAIL, LOW_SHARPE=-0.44(limit 1.25):FAIL, LOW_SUB_UNIVERSE_SHARPE=-0.84(limit -0.19):FAIL</t>
+        </is>
+      </c>
+      <c r="AO457" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP457" t="inlineStr">
+        <is>
+          <t>4/8</t>
+        </is>
+      </c>
+      <c r="AR457" t="inlineStr">
+        <is>
+          <t>LOW_GRADE</t>
+        </is>
+      </c>
+      <c r="AS457" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT457" t="inlineStr">
+        <is>
+          <t>Sharpe -0.44 &lt; 1.25; Fitness -0.20 &lt; 1.00; Positive years 1/4 = 25.0% &lt; 60.0%; Negative-sharpe years 3 &gt; 1</t>
+        </is>
+      </c>
+      <c r="AU457" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV457" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW457" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX457" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AY457" t="n">
+        <v>1.207266195446003</v>
+      </c>
+      <c r="AZ457" t="n">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:19:44+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>p36_f2_da</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>group_zscore(winsorize(-ts_mean(ts_backfill(accumulated_depreciation_depletion_amortization_ppne, 60) / cap, 20), std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>fundamental2, pv1</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>accumulated_depreciation_depletion_amortization_ppne, cap</t>
+        </is>
+      </c>
+      <c r="H458" t="n">
+        <v>2</v>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>2rOQIapr4sG9OwVaGyEynb</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>XgWVonA0</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/XgWVonA0</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N458" t="n">
+        <v>1</v>
+      </c>
+      <c r="O458" t="n">
+        <v>12</v>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q458" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T458" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V458" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W458" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="X458" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="Y458" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="Z458" t="n">
+        <v>-0.1101</v>
+      </c>
+      <c r="AA458" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="AB458" t="n">
+        <v>-0.019252</v>
+      </c>
+      <c r="AC458" t="n">
+        <v>-5446608</v>
+      </c>
+      <c r="AD458" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE458" t="n">
+        <v>1711</v>
+      </c>
+      <c r="AF458" t="n">
+        <v>718</v>
+      </c>
+      <c r="AG458" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="AH458" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="AI458" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="AJ458" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="AK458" t="n">
+        <v>-0.0529</v>
+      </c>
+      <c r="AL458" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="AM458" t="n">
+        <v>0.1122</v>
+      </c>
+      <c r="AN458" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=-0.86(limit 1.0):FAIL, LOW_SHARPE=-0.92(limit 1.25):FAIL, LOW_SUB_UNIVERSE_SHARPE=-0.53(limit -0.4):FAIL</t>
+        </is>
+      </c>
+      <c r="AO458" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP458" t="inlineStr">
+        <is>
+          <t>4/8</t>
+        </is>
+      </c>
+      <c r="AR458" t="inlineStr">
+        <is>
+          <t>LOW_GRADE</t>
+        </is>
+      </c>
+      <c r="AS458" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT458" t="inlineStr">
+        <is>
+          <t>Sharpe -0.92 &lt; 1.25; Fitness -0.86 &lt; 1.00; Positive years 1/4 = 25.0% &lt; 60.0%; Negative-sharpe years 3 &gt; 1</t>
+        </is>
+      </c>
+      <c r="AU458" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV458" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW458" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX458" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AY458" t="n">
+        <v>1.054830160104776</v>
+      </c>
+      <c r="AZ458" t="n">
+        <v>-2.19</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:29:24+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>r37_r4uo_k350_d7</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 350), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); o = group_zscore(winsorize(ts_mean(operating_income / cap, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + r + r + u + o, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, fundamental6</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_num_all, operating_income</t>
+        </is>
+      </c>
+      <c r="H459" t="n">
+        <v>5</v>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>WnS3e9im4YJ98P1go1kEYUg</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>A10eljkE</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/A10eljkE</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N459" t="n">
+        <v>1</v>
+      </c>
+      <c r="O459" t="n">
+        <v>7</v>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q459" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T459" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V459" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W459" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="X459" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Y459" t="n">
+        <v>0.0626</v>
+      </c>
+      <c r="Z459" t="n">
+        <v>0.1117</v>
+      </c>
+      <c r="AA459" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="AB459" t="n">
+        <v>0.003567</v>
+      </c>
+      <c r="AC459" t="n">
+        <v>5524998</v>
+      </c>
+      <c r="AD459" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE459" t="n">
+        <v>1412</v>
+      </c>
+      <c r="AF459" t="n">
+        <v>1332</v>
+      </c>
+      <c r="AG459" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AH459" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AI459" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AJ459" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AK459" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="AL459" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="AM459" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="AN459" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.7194(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO459" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP459" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ459" t="n">
+        <v>0.7194</v>
+      </c>
+      <c r="AR459" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS459" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU459" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV459" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW459" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX459" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY459" t="n">
+        <v>1.581020240224647</v>
+      </c>
+      <c r="AZ459" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:29:17+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>r37_r4uo_k250_d5</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 250), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); o = group_zscore(winsorize(ts_mean(operating_income / cap, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + r + r + u + o, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, fundamental6</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_num_all, operating_income</t>
+        </is>
+      </c>
+      <c r="H460" t="n">
+        <v>5</v>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>3DkLy2dEj57g90aNgoi6MwN</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>9qV8XZad</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/9qV8XZad</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N460" t="n">
+        <v>1</v>
+      </c>
+      <c r="O460" t="n">
+        <v>5</v>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q460" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T460" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V460" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W460" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X460" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Y460" t="n">
+        <v>0.0796</v>
+      </c>
+      <c r="Z460" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="AA460" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="AB460" t="n">
+        <v>0.002883</v>
+      </c>
+      <c r="AC460" t="n">
+        <v>5677177</v>
+      </c>
+      <c r="AD460" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE460" t="n">
+        <v>1403</v>
+      </c>
+      <c r="AF460" t="n">
+        <v>1341</v>
+      </c>
+      <c r="AG460" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AH460" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AI460" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ460" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK460" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="AL460" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="AM460" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="AN460" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.7441(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO460" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP460" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ460" t="n">
+        <v>0.7441</v>
+      </c>
+      <c r="AR460" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS460" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU460" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV460" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW460" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX460" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY460" t="n">
+        <v>1.437242730601434</v>
+      </c>
+      <c r="AZ460" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:29:19+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>r37_r4u2o_k250_d7</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 250), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); o = group_zscore(winsorize(ts_mean(operating_income / cap, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + r + r + u + u + o, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, fundamental6</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_num_all, operating_income</t>
+        </is>
+      </c>
+      <c r="H461" t="n">
+        <v>5</v>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>2tNYwFdR74Atbe7rFLKvYt4</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>E5vNlOqR</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/E5vNlOqR</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N461" t="n">
+        <v>1</v>
+      </c>
+      <c r="O461" t="n">
+        <v>7</v>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q461" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T461" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V461" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W461" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X461" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y461" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="Z461" t="n">
+        <v>0.1133</v>
+      </c>
+      <c r="AA461" t="n">
+        <v>0.0621</v>
+      </c>
+      <c r="AB461" t="n">
+        <v>0.003458</v>
+      </c>
+      <c r="AC461" t="n">
+        <v>5605506</v>
+      </c>
+      <c r="AD461" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE461" t="n">
+        <v>1400</v>
+      </c>
+      <c r="AF461" t="n">
+        <v>1344</v>
+      </c>
+      <c r="AG461" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH461" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI461" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AJ461" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AK461" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="AL461" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="AM461" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="AO461" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP461" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="AQ461" t="n">
+        <v>0.6593</v>
+      </c>
+      <c r="AS461" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU461" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV461" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW461" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX461" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY461" t="n">
+        <v>1.34310585336128</v>
+      </c>
+      <c r="AZ461" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:31:17+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>r37_r4uo_k500_d7</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 500), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); o = group_zscore(winsorize(ts_mean(operating_income / cap, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + r + r + u + o, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, pv13, fundamental6</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, rel_num_all, operating_income</t>
+        </is>
+      </c>
+      <c r="H462" t="n">
+        <v>5</v>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>1vPRFJgRu5c5ckwdazztb9D</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>akLe7vew</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/akLe7vew</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N462" t="n">
+        <v>1</v>
+      </c>
+      <c r="O462" t="n">
+        <v>7</v>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q462" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T462" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V462" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W462" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X462" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y462" t="n">
+        <v>0.0567</v>
+      </c>
+      <c r="Z462" t="n">
+        <v>0.1055</v>
+      </c>
+      <c r="AA462" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="AB462" t="n">
+        <v>0.003722</v>
+      </c>
+      <c r="AC462" t="n">
+        <v>5221456</v>
+      </c>
+      <c r="AD462" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE462" t="n">
+        <v>1416</v>
+      </c>
+      <c r="AF462" t="n">
+        <v>1328</v>
+      </c>
+      <c r="AG462" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH462" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AI462" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AJ462" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK462" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="AL462" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="AM462" t="n">
+        <v>0.0434</v>
+      </c>
+      <c r="AN462" t="inlineStr"/>
+      <c r="AO462" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP462" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="AQ462" t="n">
+        <v>0.6866</v>
+      </c>
+      <c r="AR462" t="inlineStr"/>
+      <c r="AS462" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT462" t="inlineStr"/>
+      <c r="AU462" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV462" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW462" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX462" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY462" t="n">
+        <v>1.655523582838171</v>
+      </c>
+      <c r="AZ462" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BA462" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/experiments.xlsx
+++ b/data/experiments.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA462"/>
+  <dimension ref="A1:BA484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82422,7 +82422,6 @@
       <c r="AM462" t="n">
         <v>0.0434</v>
       </c>
-      <c r="AN462" t="inlineStr"/>
       <c r="AO462" t="inlineStr">
         <is>
           <t>YES</t>
@@ -82436,11 +82435,9 @@
       <c r="AQ462" t="n">
         <v>0.6866</v>
       </c>
-      <c r="AR462" t="inlineStr"/>
       <c r="AS462" t="b">
         <v>1</v>
       </c>
-      <c r="AT462" t="inlineStr"/>
       <c r="AU462" t="n">
         <v>4</v>
       </c>
@@ -82459,7 +82456,4332 @@
       <c r="AZ462" t="n">
         <v>0.63</v>
       </c>
-      <c r="BA462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:15:00+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>p38_f6_assets</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>group_zscore(winsorize(ts_mean(ts_backfill(assets, 60) / cap, 20), std=3.0), subindustry)</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>fundamental6, pv1</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>assets, cap</t>
+        </is>
+      </c>
+      <c r="H463" t="n">
+        <v>2</v>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>1NY3ixaAu4It93HMjJBWHxB</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>xAYoWW6b</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/xAYoWW6b</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N463" t="n">
+        <v>1</v>
+      </c>
+      <c r="O463" t="n">
+        <v>12</v>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q463" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T463" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V463" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W463" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="X463" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="Y463" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="Z463" t="n">
+        <v>0.0887</v>
+      </c>
+      <c r="AA463" t="n">
+        <v>0.1711</v>
+      </c>
+      <c r="AB463" t="n">
+        <v>0.012897</v>
+      </c>
+      <c r="AC463" t="n">
+        <v>4390579</v>
+      </c>
+      <c r="AD463" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE463" t="n">
+        <v>1133</v>
+      </c>
+      <c r="AF463" t="n">
+        <v>1883</v>
+      </c>
+      <c r="AG463" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AH463" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AI463" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AJ463" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AK463" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="AL463" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="AM463" t="n">
+        <v>0.1136</v>
+      </c>
+      <c r="AN463" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=0.72(limit 1.0):FAIL, LOW_SHARPE=0.86(limit 1.25):FAIL</t>
+        </is>
+      </c>
+      <c r="AO463" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP463" t="inlineStr">
+        <is>
+          <t>5/8</t>
+        </is>
+      </c>
+      <c r="AR463" t="inlineStr">
+        <is>
+          <t>LOW_GRADE</t>
+        </is>
+      </c>
+      <c r="AS463" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT463" t="inlineStr">
+        <is>
+          <t>Sharpe 0.86 &lt; 1.25; Fitness 0.72 &lt; 1.00</t>
+        </is>
+      </c>
+      <c r="AU463" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV463" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW463" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX463" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY463" t="n">
+        <v>0.8990550594930212</v>
+      </c>
+      <c r="AZ463" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:15:04+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>p38_f6_debt</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>group_zscore(winsorize(-ts_mean(ts_backfill(debt, 60) / cap, 20), std=3.0), subindustry)</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>fundamental6, pv1</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>debt, cap</t>
+        </is>
+      </c>
+      <c r="H464" t="n">
+        <v>2</v>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>D0a7coJ5d2b3SdDMMKFLH</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>RRVoKKLo</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/RRVoKKLo</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N464" t="n">
+        <v>1</v>
+      </c>
+      <c r="O464" t="n">
+        <v>12</v>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q464" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V464" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W464" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="X464" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="Y464" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="Z464" t="n">
+        <v>-0.1067</v>
+      </c>
+      <c r="AA464" t="n">
+        <v>0.6074000000000001</v>
+      </c>
+      <c r="AB464" t="n">
+        <v>-0.014823</v>
+      </c>
+      <c r="AC464" t="n">
+        <v>-5281672</v>
+      </c>
+      <c r="AD464" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE464" t="n">
+        <v>1811</v>
+      </c>
+      <c r="AF464" t="n">
+        <v>977</v>
+      </c>
+      <c r="AG464" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="AH464" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AI464" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="AJ464" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AK464" t="n">
+        <v>-0.0406</v>
+      </c>
+      <c r="AL464" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="AM464" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="AN464" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=-1.03(limit 1.0):FAIL, LOW_SHARPE=-1.11(limit 1.25):FAIL, LOW_SUB_UNIVERSE_SHARPE=-0.64(limit -0.48):FAIL</t>
+        </is>
+      </c>
+      <c r="AO464" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP464" t="inlineStr">
+        <is>
+          <t>4/8</t>
+        </is>
+      </c>
+      <c r="AR464" t="inlineStr">
+        <is>
+          <t>LOW_GRADE</t>
+        </is>
+      </c>
+      <c r="AS464" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT464" t="inlineStr">
+        <is>
+          <t>Sharpe -1.11 &lt; 1.25; Fitness -1.03 &lt; 1.00; Positive years 0/4 = 0.0% &lt; 60.0%; Negative-sharpe years 4 &gt; 1</t>
+        </is>
+      </c>
+      <c r="AU464" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV464" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW464" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX464" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY464" t="n">
+        <v>0.619408319823577</v>
+      </c>
+      <c r="AZ464" t="n">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:15:21+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>p38_f6_cflow</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>group_zscore(winsorize(ts_mean(ts_backfill(cashflow_op, 60) / cap, 20), std=3.0), subindustry)</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>fundamental6, pv1</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>cashflow_op, cap</t>
+        </is>
+      </c>
+      <c r="H465" t="n">
+        <v>2</v>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>3Y7UGk9d84GMcwra01NURFy</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>E5vMLLp9</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/E5vMLLp9</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N465" t="n">
+        <v>1</v>
+      </c>
+      <c r="O465" t="n">
+        <v>12</v>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q465" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T465" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V465" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W465" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X465" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="Y465" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="Z465" t="n">
+        <v>0.0784</v>
+      </c>
+      <c r="AA465" t="n">
+        <v>0.1724</v>
+      </c>
+      <c r="AB465" t="n">
+        <v>0.009838</v>
+      </c>
+      <c r="AC465" t="n">
+        <v>3879659</v>
+      </c>
+      <c r="AD465" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE465" t="n">
+        <v>1386</v>
+      </c>
+      <c r="AF465" t="n">
+        <v>1543</v>
+      </c>
+      <c r="AG465" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AH465" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AI465" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AJ465" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AK465" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AL465" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="AM465" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="AN465" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=0.63(limit 1.0):FAIL, LOW_SHARPE=0.8(limit 1.25):FAIL</t>
+        </is>
+      </c>
+      <c r="AO465" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP465" t="inlineStr">
+        <is>
+          <t>5/8</t>
+        </is>
+      </c>
+      <c r="AR465" t="inlineStr">
+        <is>
+          <t>LOW_GRADE</t>
+        </is>
+      </c>
+      <c r="AS465" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT465" t="inlineStr">
+        <is>
+          <t>Sharpe 0.80 &lt; 1.25; Fitness 0.63 &lt; 1.00; Positive years 2/4 = 50.0% &lt; 60.0%; Negative-sharpe years 2 &gt; 1</t>
+        </is>
+      </c>
+      <c r="AU465" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV465" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW465" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX465" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY465" t="n">
+        <v>1.413915956955481</v>
+      </c>
+      <c r="AZ465" t="n">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:16:41+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>p38_f6_bvps</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>group_zscore(winsorize(ts_mean(ts_backfill(bookvalue_ps, 60), 20), std=3.0), subindustry)</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>fundamental6</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>bookvalue_ps</t>
+        </is>
+      </c>
+      <c r="H466" t="n">
+        <v>1</v>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>XYhMaPD5f1c9RQhkbbv66</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>j23JxKpe</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/j23JxKpe</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N466" t="n">
+        <v>1</v>
+      </c>
+      <c r="O466" t="n">
+        <v>12</v>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q466" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T466" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V466" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W466" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="X466" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y466" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="Z466" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="AA466" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="AB466" t="n">
+        <v>0.00361</v>
+      </c>
+      <c r="AC466" t="n">
+        <v>750454</v>
+      </c>
+      <c r="AD466" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE466" t="n">
+        <v>1111</v>
+      </c>
+      <c r="AF466" t="n">
+        <v>1795</v>
+      </c>
+      <c r="AG466" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AH466" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AI466" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AJ466" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK466" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="AL466" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="AM466" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="AN466" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=0.07(limit 1.0):FAIL, LOW_SHARPE=0.19(limit 1.25):FAIL, LOW_SUB_UNIVERSE_SHARPE=-0.1(limit 0.08):FAIL, LOW_TURNOVER=0.0084(limit 0.01):FAIL</t>
+        </is>
+      </c>
+      <c r="AO466" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP466" t="inlineStr">
+        <is>
+          <t>3/8</t>
+        </is>
+      </c>
+      <c r="AR466" t="inlineStr">
+        <is>
+          <t>LOW_GRADE</t>
+        </is>
+      </c>
+      <c r="AS466" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT466" t="inlineStr">
+        <is>
+          <t>Sharpe 0.19 &lt; 1.25; Fitness 0.07 &lt; 1.00</t>
+        </is>
+      </c>
+      <c r="AU466" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV466" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW466" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX466" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY466" t="n">
+        <v>2.065387372867376</v>
+      </c>
+      <c r="AZ466" t="n">
+        <v>-3.27</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:17:11+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>p38_f6_capex</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>group_zscore(winsorize(ts_mean(ts_backfill(capex, 60) / cap, 20), std=3.0), subindustry)</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>fundamental6, pv1</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>capex, cap</t>
+        </is>
+      </c>
+      <c r="H467" t="n">
+        <v>2</v>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>1mLEceg6K4COcjdZc55TUQb</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>rK5wVqgJ</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/rK5wVqgJ</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N467" t="n">
+        <v>1</v>
+      </c>
+      <c r="O467" t="n">
+        <v>12</v>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q467" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T467" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U467" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V467" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W467" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="X467" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="Y467" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="Z467" t="n">
+        <v>0.0829</v>
+      </c>
+      <c r="AA467" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="AB467" t="n">
+        <v>0.012698</v>
+      </c>
+      <c r="AC467" t="n">
+        <v>4103063</v>
+      </c>
+      <c r="AD467" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE467" t="n">
+        <v>918</v>
+      </c>
+      <c r="AF467" t="n">
+        <v>1907</v>
+      </c>
+      <c r="AG467" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AH467" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AI467" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ467" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AK467" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="AL467" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="AM467" t="n">
+        <v>0.0823</v>
+      </c>
+      <c r="AN467" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=0.81(limit 1.0):FAIL, LOW_SHARPE=0.99(limit 1.25):FAIL</t>
+        </is>
+      </c>
+      <c r="AO467" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP467" t="inlineStr">
+        <is>
+          <t>5/8</t>
+        </is>
+      </c>
+      <c r="AR467" t="inlineStr">
+        <is>
+          <t>LOW_GRADE</t>
+        </is>
+      </c>
+      <c r="AS467" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT467" t="inlineStr">
+        <is>
+          <t>Sharpe 0.99 &lt; 1.25; Fitness 0.81 &lt; 1.00</t>
+        </is>
+      </c>
+      <c r="AU467" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV467" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW467" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX467" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY467" t="n">
+        <v>1.236513916891624</v>
+      </c>
+      <c r="AZ467" t="n">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>p38_f6_cogs</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>group_zscore(winsorize(-ts_mean(ts_backfill(cogs, 60) / cap, 20), std=3.0), subindustry)</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>fundamental6, pv1</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>cogs, cap</t>
+        </is>
+      </c>
+      <c r="H468" t="n">
+        <v>2</v>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>13ny8FaOc4DT8ZE9NS6coDs</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>kqVMOwld</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/kqVMOwld</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N468" t="n">
+        <v>1</v>
+      </c>
+      <c r="O468" t="n">
+        <v>12</v>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q468" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T468" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U468" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V468" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W468" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="X468" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="Y468" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="Z468" t="n">
+        <v>-0.0953</v>
+      </c>
+      <c r="AA468" t="n">
+        <v>0.5760999999999999</v>
+      </c>
+      <c r="AB468" t="n">
+        <v>-0.013216</v>
+      </c>
+      <c r="AC468" t="n">
+        <v>-4713915</v>
+      </c>
+      <c r="AD468" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE468" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AF468" t="n">
+        <v>1027</v>
+      </c>
+      <c r="AG468" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="AH468" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AI468" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="AJ468" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="AK468" t="n">
+        <v>-0.0852</v>
+      </c>
+      <c r="AL468" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AM468" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="AN468" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=-0.93(limit 1.0):FAIL, LOW_SHARPE=-1.07(limit 1.25):FAIL, LOW_SUB_UNIVERSE_SHARPE=-0.49(limit -0.46):FAIL</t>
+        </is>
+      </c>
+      <c r="AO468" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP468" t="inlineStr">
+        <is>
+          <t>4/8</t>
+        </is>
+      </c>
+      <c r="AR468" t="inlineStr">
+        <is>
+          <t>LOW_GRADE</t>
+        </is>
+      </c>
+      <c r="AS468" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT468" t="inlineStr">
+        <is>
+          <t>Sharpe -1.07 &lt; 1.25; Fitness -0.93 &lt; 1.00; Positive years 1/4 = 25.0% &lt; 60.0%; Negative-sharpe years 3 &gt; 1</t>
+        </is>
+      </c>
+      <c r="AU468" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV468" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW468" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX468" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AY468" t="n">
+        <v>1.00619332138511</v>
+      </c>
+      <c r="AZ468" t="n">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:18:25+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>p38_a4_eps</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>group_zscore(winsorize(ts_mean(ts_backfill(actual_eps_value_quarterly, 40) / cap, 20), std=3.0), subindustry)</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>analyst4, pv1</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>actual_eps_value_quarterly, cap</t>
+        </is>
+      </c>
+      <c r="H469" t="n">
+        <v>2</v>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>5SonpdCI4ZIane18nzPtArx</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>LL9w3Pm9</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/LL9w3Pm9</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N469" t="n">
+        <v>1</v>
+      </c>
+      <c r="O469" t="n">
+        <v>12</v>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q469" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T469" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U469" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V469" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W469" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X469" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Y469" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="Z469" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="AA469" t="n">
+        <v>0.2427</v>
+      </c>
+      <c r="AB469" t="n">
+        <v>0.003565</v>
+      </c>
+      <c r="AC469" t="n">
+        <v>2058188</v>
+      </c>
+      <c r="AD469" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE469" t="n">
+        <v>1406</v>
+      </c>
+      <c r="AF469" t="n">
+        <v>1593</v>
+      </c>
+      <c r="AG469" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AH469" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AI469" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AJ469" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AK469" t="n">
+        <v>-0.0209</v>
+      </c>
+      <c r="AL469" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="AM469" t="n">
+        <v>0.0861</v>
+      </c>
+      <c r="AN469" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=0.29(limit 1.0):FAIL, LOW_SHARPE=0.5(limit 1.25):FAIL, LOW_SUB_UNIVERSE_SHARPE=-0.05(limit 0.22):FAIL</t>
+        </is>
+      </c>
+      <c r="AO469" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP469" t="inlineStr">
+        <is>
+          <t>4/8</t>
+        </is>
+      </c>
+      <c r="AR469" t="inlineStr">
+        <is>
+          <t>LOW_GRADE</t>
+        </is>
+      </c>
+      <c r="AS469" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT469" t="inlineStr">
+        <is>
+          <t>Sharpe 0.50 &lt; 1.25; Fitness 0.29 &lt; 1.00; Positive years 2/4 = 50.0% &lt; 60.0%; Negative-sharpe years 2 &gt; 1</t>
+        </is>
+      </c>
+      <c r="AU469" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV469" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW469" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX469" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY469" t="n">
+        <v>2.775036035802058</v>
+      </c>
+      <c r="AZ469" t="n">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:18:42+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>p38_a4_adjni</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>group_zscore(winsorize(ts_mean(ts_backfill(adj_net_income_avg, 40) / cap, 20), std=3.0), subindustry)</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>analyst4, pv1</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>adj_net_income_avg, cap</t>
+        </is>
+      </c>
+      <c r="H470" t="n">
+        <v>2</v>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>3qOH2AdVo4kEcjiiw6KEvvA</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>ZY09NYd8</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/ZY09NYd8</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N470" t="n">
+        <v>1</v>
+      </c>
+      <c r="O470" t="n">
+        <v>12</v>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q470" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T470" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U470" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V470" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W470" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="X470" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="Y470" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="Z470" t="n">
+        <v>0.0646</v>
+      </c>
+      <c r="AA470" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="AB470" t="n">
+        <v>0.007467</v>
+      </c>
+      <c r="AC470" t="n">
+        <v>3194042</v>
+      </c>
+      <c r="AD470" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE470" t="n">
+        <v>1194</v>
+      </c>
+      <c r="AF470" t="n">
+        <v>1429</v>
+      </c>
+      <c r="AG470" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AH470" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AI470" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ470" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AK470" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="AL470" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="AM470" t="n">
+        <v>0.0593</v>
+      </c>
+      <c r="AN470" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=0.62(limit 1.0):FAIL, LOW_SHARPE=0.86(limit 1.25):FAIL, LOW_SUB_UNIVERSE_SHARPE=0.29(limit 0.37):FAIL</t>
+        </is>
+      </c>
+      <c r="AO470" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP470" t="inlineStr">
+        <is>
+          <t>4/8</t>
+        </is>
+      </c>
+      <c r="AR470" t="inlineStr">
+        <is>
+          <t>LOW_GRADE</t>
+        </is>
+      </c>
+      <c r="AS470" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT470" t="inlineStr">
+        <is>
+          <t>Sharpe 0.86 &lt; 1.25; Fitness 0.62 &lt; 1.00</t>
+        </is>
+      </c>
+      <c r="AU470" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV470" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW470" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX470" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY470" t="n">
+        <v>1.299923074647112</v>
+      </c>
+      <c r="AZ470" t="n">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:19:04+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>p38_o9_be180</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>group_zscore(winsorize(ts_mean(call_breakeven_180 / close, 20), std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>option9, pv1</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>call_breakeven_180, close</t>
+        </is>
+      </c>
+      <c r="H471" t="n">
+        <v>2</v>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>4x0tipc2P5eead8dF7lfzMb</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>xAYo5O1n</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/xAYo5O1n</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N471" t="n">
+        <v>1</v>
+      </c>
+      <c r="O471" t="n">
+        <v>12</v>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q471" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T471" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U471" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V471" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W471" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X471" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Y471" t="n">
+        <v>0.0359</v>
+      </c>
+      <c r="Z471" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="AA471" t="n">
+        <v>0.7968</v>
+      </c>
+      <c r="AB471" t="n">
+        <v>0.000831</v>
+      </c>
+      <c r="AC471" t="n">
+        <v>738315</v>
+      </c>
+      <c r="AD471" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE471" t="n">
+        <v>1131</v>
+      </c>
+      <c r="AF471" t="n">
+        <v>1822</v>
+      </c>
+      <c r="AG471" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AH471" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI471" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AJ471" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AK471" t="n">
+        <v>0.0859</v>
+      </c>
+      <c r="AL471" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="AM471" t="n">
+        <v>0.2445</v>
+      </c>
+      <c r="AN471" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=0.02(limit 1.0):FAIL, LOW_SHARPE=0.07(limit 1.25):FAIL</t>
+        </is>
+      </c>
+      <c r="AO471" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP471" t="inlineStr">
+        <is>
+          <t>5/8</t>
+        </is>
+      </c>
+      <c r="AR471" t="inlineStr">
+        <is>
+          <t>LOW_GRADE</t>
+        </is>
+      </c>
+      <c r="AS471" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT471" t="inlineStr">
+        <is>
+          <t>Sharpe 0.07 &lt; 1.25; Fitness 0.02 &lt; 1.00; Positive years 2/4 = 50.0% &lt; 60.0%; Negative-sharpe years 2 &gt; 1</t>
+        </is>
+      </c>
+      <c r="AU471" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV471" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW471" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX471" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY471" t="n">
+        <v>1.511210883144154</v>
+      </c>
+      <c r="AZ471" t="n">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:20:11+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>p38_o9_fp120</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>group_zscore(winsorize(ts_mean(forward_price_120 / close, 20), std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>option9, pv1</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>forward_price_120, close</t>
+        </is>
+      </c>
+      <c r="H472" t="n">
+        <v>2</v>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>1mZeqL48x5iB8xBBBIUvH02</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>ZY09N3vd</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/ZY09N3vd</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N472" t="n">
+        <v>1</v>
+      </c>
+      <c r="O472" t="n">
+        <v>12</v>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q472" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T472" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U472" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V472" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W472" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X472" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Y472" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="Z472" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="AA472" t="n">
+        <v>0.1196</v>
+      </c>
+      <c r="AB472" t="n">
+        <v>0.001667</v>
+      </c>
+      <c r="AC472" t="n">
+        <v>1258247</v>
+      </c>
+      <c r="AD472" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE472" t="n">
+        <v>1114</v>
+      </c>
+      <c r="AF472" t="n">
+        <v>1836</v>
+      </c>
+      <c r="AG472" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AH472" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI472" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AJ472" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AK472" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="AL472" t="n">
+        <v>0.0261</v>
+      </c>
+      <c r="AM472" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="AN472" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=0.14(limit 1.0):FAIL, LOW_SHARPE=0.3(limit 1.25):FAIL</t>
+        </is>
+      </c>
+      <c r="AO472" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP472" t="inlineStr">
+        <is>
+          <t>5/8</t>
+        </is>
+      </c>
+      <c r="AR472" t="inlineStr">
+        <is>
+          <t>LOW_GRADE</t>
+        </is>
+      </c>
+      <c r="AS472" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT472" t="inlineStr">
+        <is>
+          <t>Sharpe 0.30 &lt; 1.25; Fitness 0.14 &lt; 1.00</t>
+        </is>
+      </c>
+      <c r="AU472" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV472" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW472" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX472" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY472" t="n">
+        <v>0.4057914078275521</v>
+      </c>
+      <c r="AZ472" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:20:29+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>p38_o8_ivc180</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>group_zscore(winsorize(-ts_mean(implied_volatility_call_180, 20), std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>option8</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>implied_volatility_call_180</t>
+        </is>
+      </c>
+      <c r="H473" t="n">
+        <v>1</v>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>2FkL3L2D85jRavxV30AVNTq</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>kqVM92ZK</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/kqVM92ZK</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N473" t="n">
+        <v>1</v>
+      </c>
+      <c r="O473" t="n">
+        <v>12</v>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q473" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T473" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V473" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W473" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="X473" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y473" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="Z473" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="AA473" t="n">
+        <v>0.8554</v>
+      </c>
+      <c r="AB473" t="n">
+        <v>-0.000217</v>
+      </c>
+      <c r="AC473" t="n">
+        <v>-104305</v>
+      </c>
+      <c r="AD473" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE473" t="n">
+        <v>1708</v>
+      </c>
+      <c r="AF473" t="n">
+        <v>1223</v>
+      </c>
+      <c r="AG473" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AH473" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AI473" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="AJ473" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AK473" t="n">
+        <v>-0.0866</v>
+      </c>
+      <c r="AL473" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="AM473" t="n">
+        <v>0.2088</v>
+      </c>
+      <c r="AN473" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=-0.0(limit 1.0):FAIL, LOW_SHARPE=-0.01(limit 1.25):FAIL, LOW_SUB_UNIVERSE_SHARPE=-0.12(limit -0.0):FAIL</t>
+        </is>
+      </c>
+      <c r="AO473" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP473" t="inlineStr">
+        <is>
+          <t>4/8</t>
+        </is>
+      </c>
+      <c r="AR473" t="inlineStr">
+        <is>
+          <t>LOW_GRADE</t>
+        </is>
+      </c>
+      <c r="AS473" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT473" t="inlineStr">
+        <is>
+          <t>Sharpe -0.01 &lt; 1.25; Fitness -0.00 &lt; 1.00</t>
+        </is>
+      </c>
+      <c r="AU473" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV473" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW473" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX473" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY473" t="n">
+        <v>1.513370961353054</v>
+      </c>
+      <c r="AZ473" t="n">
+        <v>-2.33</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:20:49+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>p38_o8_hv120</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>INFERIOR</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>group_zscore(winsorize(-ts_mean(historical_volatility_120, 20), std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>option8</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>historical_volatility_120</t>
+        </is>
+      </c>
+      <c r="H474" t="n">
+        <v>1</v>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>37LYh04cr4OIaFNPU9tRJDr</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>j23JOmnQ</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/j23JOmnQ</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N474" t="n">
+        <v>1</v>
+      </c>
+      <c r="O474" t="n">
+        <v>12</v>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q474" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T474" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U474" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V474" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W474" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X474" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y474" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="Z474" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AA474" t="n">
+        <v>0.7933</v>
+      </c>
+      <c r="AB474" t="n">
+        <v>0.000521</v>
+      </c>
+      <c r="AC474" t="n">
+        <v>248610</v>
+      </c>
+      <c r="AD474" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE474" t="n">
+        <v>1759</v>
+      </c>
+      <c r="AF474" t="n">
+        <v>1201</v>
+      </c>
+      <c r="AG474" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AH474" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AI474" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="AJ474" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="AK474" t="n">
+        <v>-0.0432</v>
+      </c>
+      <c r="AL474" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="AM474" t="n">
+        <v>0.1917</v>
+      </c>
+      <c r="AN474" t="inlineStr">
+        <is>
+          <t>LOW_FITNESS=0.0(limit 1.0):FAIL, LOW_SHARPE=0.02(limit 1.25):FAIL, LOW_SUB_UNIVERSE_SHARPE=-0.02(limit 0.01):FAIL</t>
+        </is>
+      </c>
+      <c r="AO474" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP474" t="inlineStr">
+        <is>
+          <t>4/8</t>
+        </is>
+      </c>
+      <c r="AR474" t="inlineStr">
+        <is>
+          <t>LOW_GRADE</t>
+        </is>
+      </c>
+      <c r="AS474" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT474" t="inlineStr">
+        <is>
+          <t>Sharpe 0.02 &lt; 1.25; Fitness 0.00 &lt; 1.00</t>
+        </is>
+      </c>
+      <c r="AU474" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV474" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW474" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX474" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY474" t="n">
+        <v>1.359963234797176</v>
+      </c>
+      <c r="AZ474" t="n">
+        <v>-1.99</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:28:36+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>r39_r3d2u_k250_d7</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 250), std=3.0), subindustry); d = group_zscore(winsorize(ts_mean(ts_backfill(debt, 60) / cap, 20), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); group_zscore(winsorize(r + r + r + d + d + u, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, fundamental6, pv13</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, debt, rel_num_all</t>
+        </is>
+      </c>
+      <c r="H475" t="n">
+        <v>5</v>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>26QxnsXI4PGceX3gGPhs2W</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>LL9w3KJm</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/LL9w3KJm</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N475" t="n">
+        <v>1</v>
+      </c>
+      <c r="O475" t="n">
+        <v>7</v>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q475" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T475" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U475" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V475" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W475" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="X475" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Y475" t="n">
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="Z475" t="n">
+        <v>0.1401</v>
+      </c>
+      <c r="AA475" t="n">
+        <v>0.0578</v>
+      </c>
+      <c r="AB475" t="n">
+        <v>0.004398</v>
+      </c>
+      <c r="AC475" t="n">
+        <v>6931935</v>
+      </c>
+      <c r="AD475" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE475" t="n">
+        <v>1285</v>
+      </c>
+      <c r="AF475" t="n">
+        <v>1289</v>
+      </c>
+      <c r="AG475" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH475" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AI475" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AJ475" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AK475" t="n">
+        <v>0.0359</v>
+      </c>
+      <c r="AL475" t="n">
+        <v>0.0622</v>
+      </c>
+      <c r="AM475" t="n">
+        <v>0.0473</v>
+      </c>
+      <c r="AO475" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP475" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="AQ475" t="n">
+        <v>0.6536</v>
+      </c>
+      <c r="AS475" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU475" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV475" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW475" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX475" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY475" t="n">
+        <v>1.03512881646038</v>
+      </c>
+      <c r="AZ475" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:28:43+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>r39_r3d2g_k250_d7</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 250), std=3.0), subindustry); d = group_zscore(winsorize(ts_mean(ts_backfill(debt, 60) / cap, 20), std=3.0), subindustry); g = group_zscore(winsorize(ts_mean(ts_backfill(cogs, 60) / cap, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + r + d + d + g, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, fundamental6</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, debt, cogs</t>
+        </is>
+      </c>
+      <c r="H476" t="n">
+        <v>5</v>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>1eX0uKgfv5gWass18OYTcSwc</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>gJQ5LavK</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/gJQ5LavK</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N476" t="n">
+        <v>1</v>
+      </c>
+      <c r="O476" t="n">
+        <v>7</v>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q476" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T476" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V476" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W476" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X476" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y476" t="n">
+        <v>0.0613</v>
+      </c>
+      <c r="Z476" t="n">
+        <v>0.1457</v>
+      </c>
+      <c r="AA476" t="n">
+        <v>0.1039</v>
+      </c>
+      <c r="AB476" t="n">
+        <v>0.00475</v>
+      </c>
+      <c r="AC476" t="n">
+        <v>7208409</v>
+      </c>
+      <c r="AD476" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE476" t="n">
+        <v>1263</v>
+      </c>
+      <c r="AF476" t="n">
+        <v>1308</v>
+      </c>
+      <c r="AG476" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH476" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AI476" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AJ476" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AK476" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="AL476" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AM476" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="AO476" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP476" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="AQ476" t="n">
+        <v>0.5581</v>
+      </c>
+      <c r="AS476" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU476" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV476" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW476" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX476" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY476" t="n">
+        <v>1.140186388271672</v>
+      </c>
+      <c r="AZ476" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:28:18+00:00</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>r39_r3g2u_k250_d7</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 250), std=3.0), subindustry); g = group_zscore(winsorize(ts_mean(ts_backfill(cogs, 60) / cap, 20), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); group_zscore(winsorize(r + r + r + g + g + u, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, fundamental6, pv13</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, cogs, rel_num_all</t>
+        </is>
+      </c>
+      <c r="H477" t="n">
+        <v>5</v>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>4f0534bF24pi9CaXViUkv4D</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>2rOxeAvJ</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/2rOxeAvJ</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N477" t="n">
+        <v>1</v>
+      </c>
+      <c r="O477" t="n">
+        <v>7</v>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q477" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T477" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V477" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W477" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X477" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Y477" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="Z477" t="n">
+        <v>0.1369</v>
+      </c>
+      <c r="AA477" t="n">
+        <v>0.0771</v>
+      </c>
+      <c r="AB477" t="n">
+        <v>0.004311</v>
+      </c>
+      <c r="AC477" t="n">
+        <v>6772175</v>
+      </c>
+      <c r="AD477" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE477" t="n">
+        <v>1383</v>
+      </c>
+      <c r="AF477" t="n">
+        <v>1379</v>
+      </c>
+      <c r="AG477" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AH477" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AI477" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AJ477" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AK477" t="n">
+        <v>0.0544</v>
+      </c>
+      <c r="AL477" t="n">
+        <v>0.0621</v>
+      </c>
+      <c r="AM477" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="AO477" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP477" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="AQ477" t="n">
+        <v>0.6753</v>
+      </c>
+      <c r="AS477" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU477" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV477" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW477" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX477" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY477" t="n">
+        <v>1.444538565309583</v>
+      </c>
+      <c r="AZ477" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:30:07+00:00</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>r39_r4d2u_k250_d7</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 250), std=3.0), subindustry); d = group_zscore(winsorize(ts_mean(ts_backfill(debt, 60) / cap, 20), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); group_zscore(winsorize(r + r + r + r + d + d + u, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, fundamental6, pv13</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, debt, rel_num_all</t>
+        </is>
+      </c>
+      <c r="H478" t="n">
+        <v>5</v>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>3eH7MQ8KV5k6cpmgXqOgSbl</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>vRkbPGlr</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/vRkbPGlr</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N478" t="n">
+        <v>1</v>
+      </c>
+      <c r="O478" t="n">
+        <v>7</v>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q478" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V478" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W478" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="X478" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y478" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="Z478" t="n">
+        <v>0.1351</v>
+      </c>
+      <c r="AA478" t="n">
+        <v>0.0523</v>
+      </c>
+      <c r="AB478" t="n">
+        <v>0.004013</v>
+      </c>
+      <c r="AC478" t="n">
+        <v>6685932</v>
+      </c>
+      <c r="AD478" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE478" t="n">
+        <v>1303</v>
+      </c>
+      <c r="AF478" t="n">
+        <v>1271</v>
+      </c>
+      <c r="AG478" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH478" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AI478" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AJ478" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AK478" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="AL478" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="AM478" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AN478" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.7076(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO478" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP478" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ478" t="n">
+        <v>0.7076</v>
+      </c>
+      <c r="AR478" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS478" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU478" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV478" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW478" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX478" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY478" t="n">
+        <v>1.121695145750395</v>
+      </c>
+      <c r="AZ478" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:30:29+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>r39_r4g2u_k250_d7</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 250), std=3.0), subindustry); g = group_zscore(winsorize(ts_mean(ts_backfill(cogs, 60) / cap, 20), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); group_zscore(winsorize(r + r + r + r + g + g + u, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, fundamental6, pv13</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, cogs, rel_num_all</t>
+        </is>
+      </c>
+      <c r="H479" t="n">
+        <v>5</v>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>3mi9DG4fv4QZani1flTLECeh</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>d5O6vo1K</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/d5O6vo1K</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N479" t="n">
+        <v>1</v>
+      </c>
+      <c r="O479" t="n">
+        <v>7</v>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q479" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T479" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V479" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W479" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X479" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y479" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="Z479" t="n">
+        <v>0.1324</v>
+      </c>
+      <c r="AA479" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="AB479" t="n">
+        <v>0.003952</v>
+      </c>
+      <c r="AC479" t="n">
+        <v>6549939</v>
+      </c>
+      <c r="AD479" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE479" t="n">
+        <v>1400</v>
+      </c>
+      <c r="AF479" t="n">
+        <v>1362</v>
+      </c>
+      <c r="AG479" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AH479" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AI479" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AJ479" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AK479" t="n">
+        <v>0.0468</v>
+      </c>
+      <c r="AL479" t="n">
+        <v>0.0653</v>
+      </c>
+      <c r="AM479" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="AN479" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION=0.7254(limit 0.7):FAIL</t>
+        </is>
+      </c>
+      <c r="AO479" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP479" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="AQ479" t="n">
+        <v>0.7254</v>
+      </c>
+      <c r="AR479" t="inlineStr">
+        <is>
+          <t>SELF_CORRELATION_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AS479" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU479" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV479" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW479" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX479" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY479" t="n">
+        <v>1.476310152598927</v>
+      </c>
+      <c r="AZ479" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:31:02+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>r39_r4d2g_k250_d7</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 250), std=3.0), subindustry); d = group_zscore(winsorize(ts_mean(ts_backfill(debt, 60) / cap, 20), std=3.0), subindustry); g = group_zscore(winsorize(ts_mean(ts_backfill(cogs, 60) / cap, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + r + r + d + d + g, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, fundamental6</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, debt, cogs</t>
+        </is>
+      </c>
+      <c r="H480" t="n">
+        <v>5</v>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>1HZQ9M70C4j893686UJkKUp</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>qMWpVVQj</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/qMWpVVQj</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N480" t="n">
+        <v>1</v>
+      </c>
+      <c r="O480" t="n">
+        <v>7</v>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q480" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T480" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U480" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V480" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W480" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X480" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y480" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="Z480" t="n">
+        <v>0.1409</v>
+      </c>
+      <c r="AA480" t="n">
+        <v>0.09030000000000001</v>
+      </c>
+      <c r="AB480" t="n">
+        <v>0.004301</v>
+      </c>
+      <c r="AC480" t="n">
+        <v>6970734</v>
+      </c>
+      <c r="AD480" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE480" t="n">
+        <v>1288</v>
+      </c>
+      <c r="AF480" t="n">
+        <v>1284</v>
+      </c>
+      <c r="AG480" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AH480" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AI480" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AJ480" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AK480" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="AL480" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="AM480" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="AO480" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP480" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="AQ480" t="n">
+        <v>0.6155</v>
+      </c>
+      <c r="AS480" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU480" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV480" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW480" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX480" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY480" t="n">
+        <v>1.172358733494147</v>
+      </c>
+      <c r="AZ480" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:32:08+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>r39_r3d2gu_k250_d7</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 250), std=3.0), subindustry); d = group_zscore(winsorize(ts_mean(ts_backfill(debt, 60) / cap, 20), std=3.0), subindustry); g = group_zscore(winsorize(ts_mean(ts_backfill(cogs, 60) / cap, 20), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); group_zscore(winsorize(r + r + r + d + d + g + u, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, fundamental6, pv13</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, debt, cogs, rel_num_all</t>
+        </is>
+      </c>
+      <c r="H481" t="n">
+        <v>6</v>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>270GftH65k78OM132jeZKu0</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>XgWxMZg1</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/XgWxMZg1</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N481" t="n">
+        <v>1</v>
+      </c>
+      <c r="O481" t="n">
+        <v>7</v>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q481" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T481" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V481" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W481" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X481" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Y481" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="Z481" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="AA481" t="n">
+        <v>0.0863</v>
+      </c>
+      <c r="AB481" t="n">
+        <v>0.00503</v>
+      </c>
+      <c r="AC481" t="n">
+        <v>7398221</v>
+      </c>
+      <c r="AD481" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE481" t="n">
+        <v>1254</v>
+      </c>
+      <c r="AF481" t="n">
+        <v>1318</v>
+      </c>
+      <c r="AG481" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH481" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AI481" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AJ481" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AK481" t="n">
+        <v>0.0484</v>
+      </c>
+      <c r="AL481" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="AM481" t="n">
+        <v>0.0603</v>
+      </c>
+      <c r="AO481" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP481" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="AQ481" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="AS481" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU481" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV481" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW481" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX481" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY481" t="n">
+        <v>1.130998821101655</v>
+      </c>
+      <c r="AZ481" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:32:57+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>r39_r4d2gu_k250_d7</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 250), std=3.0), subindustry); d = group_zscore(winsorize(ts_mean(ts_backfill(debt, 60) / cap, 20), std=3.0), subindustry); g = group_zscore(winsorize(ts_mean(ts_backfill(cogs, 60) / cap, 20), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); group_zscore(winsorize(r + r + r + r + d + d + g + u, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, fundamental6, pv13</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, debt, cogs, rel_num_all</t>
+        </is>
+      </c>
+      <c r="H482" t="n">
+        <v>6</v>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>2r40Xd3t4tA8JNS8vge3QK</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>WjPRJ53N</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/WjPRJ53N</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N482" t="n">
+        <v>1</v>
+      </c>
+      <c r="O482" t="n">
+        <v>7</v>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q482" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V482" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W482" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="X482" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y482" t="n">
+        <v>0.0644</v>
+      </c>
+      <c r="Z482" t="n">
+        <v>0.1454</v>
+      </c>
+      <c r="AA482" t="n">
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="AB482" t="n">
+        <v>0.004514</v>
+      </c>
+      <c r="AC482" t="n">
+        <v>7192716</v>
+      </c>
+      <c r="AD482" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE482" t="n">
+        <v>1285</v>
+      </c>
+      <c r="AF482" t="n">
+        <v>1286</v>
+      </c>
+      <c r="AG482" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AH482" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AI482" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AJ482" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AK482" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="AL482" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="AM482" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="AO482" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP482" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="AQ482" t="n">
+        <v>0.6446</v>
+      </c>
+      <c r="AS482" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU482" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV482" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW482" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX482" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY482" t="n">
+        <v>1.197900941925778</v>
+      </c>
+      <c r="AZ482" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:32:52+00:00</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>r39_r3d2g_k500_d7</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 500), std=3.0), subindustry); d = group_zscore(winsorize(ts_mean(ts_backfill(debt, 60) / cap, 20), std=3.0), subindustry); g = group_zscore(winsorize(ts_mean(ts_backfill(cogs, 60) / cap, 20), std=3.0), subindustry); group_zscore(winsorize(r + r + r + d + d + g, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, fundamental6</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, debt, cogs</t>
+        </is>
+      </c>
+      <c r="H483" t="n">
+        <v>5</v>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>3WXMqLgoz4qO9Jzsix4Fifc</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>883ZXw9m</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/883ZXw9m</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N483" t="n">
+        <v>1</v>
+      </c>
+      <c r="O483" t="n">
+        <v>7</v>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q483" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U483" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V483" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W483" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X483" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Y483" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="Z483" t="n">
+        <v>0.1398</v>
+      </c>
+      <c r="AA483" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="AB483" t="n">
+        <v>0.005478</v>
+      </c>
+      <c r="AC483" t="n">
+        <v>6917154</v>
+      </c>
+      <c r="AD483" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE483" t="n">
+        <v>1266</v>
+      </c>
+      <c r="AF483" t="n">
+        <v>1306</v>
+      </c>
+      <c r="AG483" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH483" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI483" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AJ483" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AK483" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="AL483" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="AM483" t="n">
+        <v>0.0603</v>
+      </c>
+      <c r="AO483" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP483" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="AQ483" t="n">
+        <v>0.5274</v>
+      </c>
+      <c r="AS483" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU483" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV483" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW483" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX483" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY483" t="n">
+        <v>1.177398261705302</v>
+      </c>
+      <c r="AZ483" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:33:41+00:00</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>r39_r3d2xu_k250_d7</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>ey = ts_backfill(anl4_ebit_value, 40) / cap; np = ts_backfill(anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, 40) / cap; s = ey + np; r = group_zscore(winsorize(ts_rank(s, 250), std=3.0), subindustry); d = group_zscore(winsorize(ts_mean(ts_backfill(debt, 60) / cap, 20), std=3.0), subindustry); x = group_zscore(winsorize(ts_mean(ts_backfill(capex, 60) / cap, 20), std=3.0), subindustry); u = group_zscore(winsorize(ts_mean(rel_num_all, 10), std=3.0), industry); group_zscore(winsorize(r + r + r + d + d + x + u, std=3.0), industry)</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>analyst4, pv1, fundamental6, pv13</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>anl4_ebit_value, cap, anl4_fs_detail_estimates_advanced_af_nd_netprofit_mean, debt, capex, rel_num_all</t>
+        </is>
+      </c>
+      <c r="H484" t="n">
+        <v>6</v>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>4ApirH2Rw4V68Hg56L0IHBT</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>9qV32zMq</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>https://platform.worldquantbrain.com/alpha/9qV32zMq</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>TOP3000</t>
+        </is>
+      </c>
+      <c r="N484" t="n">
+        <v>1</v>
+      </c>
+      <c r="O484" t="n">
+        <v>7</v>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q484" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="U484" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="V484" t="inlineStr">
+        <is>
+          <t>FASTEXPR</t>
+        </is>
+      </c>
+      <c r="W484" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X484" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Y484" t="n">
+        <v>0.0593</v>
+      </c>
+      <c r="Z484" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="AA484" t="n">
+        <v>0.0814</v>
+      </c>
+      <c r="AB484" t="n">
+        <v>0.004888</v>
+      </c>
+      <c r="AC484" t="n">
+        <v>7166077</v>
+      </c>
+      <c r="AD484" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AE484" t="n">
+        <v>1211</v>
+      </c>
+      <c r="AF484" t="n">
+        <v>1267</v>
+      </c>
+      <c r="AG484" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH484" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI484" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AJ484" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AK484" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="AL484" t="n">
+        <v>0.0584</v>
+      </c>
+      <c r="AM484" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="AN484" t="inlineStr"/>
+      <c r="AO484" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP484" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="AQ484" t="n">
+        <v>0.5790999999999999</v>
+      </c>
+      <c r="AR484" t="inlineStr"/>
+      <c r="AS484" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT484" t="inlineStr"/>
+      <c r="AU484" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV484" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW484" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX484" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY484" t="n">
+        <v>1.083297435302666</v>
+      </c>
+      <c r="AZ484" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BA484" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
